--- a/output_data/charts/0500000US39159.xlsx
+++ b/output_data/charts/0500000US39159.xlsx
@@ -161,10 +161,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$13</c:f>
+              <c:f>Sheet1!$A$2:$A$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>2012</c:v>
                 </c:pt>
@@ -200,51 +200,57 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$13</c:f>
+              <c:f>Sheet1!$B$2:$B$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>2.905082031322743</c:v>
+                  <c:v>2.92184211996499</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.142051443258936</c:v>
+                  <c:v>3.143549252020193</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.131042557343314</c:v>
+                  <c:v>3.05919710489436</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.316607093758592</c:v>
+                  <c:v>3.299422601044817</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>3.466348227020931</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.651260899567154</c:v>
+                  <c:v>3.607051000564582</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.81252732155124</c:v>
+                  <c:v>3.825017173546494</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.091835671879418</c:v>
+                  <c:v>4.017438659663428</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4.099362800799735</c:v>
+                  <c:v>4.226935471782958</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>4.844165425465277</c:v>
+                  <c:v>4.800456576511365</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>5.146020560328332</c:v>
+                  <c:v>5.206065164891721</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>5.410905801783176</c:v>
+                  <c:v>5.375371495025197</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5.42670428512865</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -670,7 +676,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.7109375" style="1" customWidth="1"/>
@@ -689,7 +695,7 @@
         <v>2012</v>
       </c>
       <c r="B2" s="1">
-        <v>2.905082031322743</v>
+        <v>2.92184211996499</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -697,7 +703,7 @@
         <v>2013</v>
       </c>
       <c r="B3" s="1">
-        <v>3.142051443258936</v>
+        <v>3.143549252020193</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -705,7 +711,7 @@
         <v>2014</v>
       </c>
       <c r="B4" s="1">
-        <v>3.131042557343314</v>
+        <v>3.05919710489436</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -713,7 +719,7 @@
         <v>2015</v>
       </c>
       <c r="B5" s="1">
-        <v>3.316607093758592</v>
+        <v>3.299422601044817</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -729,7 +735,7 @@
         <v>2017</v>
       </c>
       <c r="B7" s="1">
-        <v>3.651260899567154</v>
+        <v>3.607051000564582</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -737,7 +743,7 @@
         <v>2018</v>
       </c>
       <c r="B8" s="1">
-        <v>3.81252732155124</v>
+        <v>3.825017173546494</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -745,7 +751,7 @@
         <v>2019</v>
       </c>
       <c r="B9" s="1">
-        <v>4.091835671879418</v>
+        <v>4.017438659663428</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -753,7 +759,7 @@
         <v>2020</v>
       </c>
       <c r="B10" s="1">
-        <v>4.099362800799735</v>
+        <v>4.226935471782958</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -761,7 +767,7 @@
         <v>2021</v>
       </c>
       <c r="B11" s="1">
-        <v>4.844165425465277</v>
+        <v>4.800456576511365</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -769,7 +775,7 @@
         <v>2022</v>
       </c>
       <c r="B12" s="1">
-        <v>5.146020560328332</v>
+        <v>5.206065164891721</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -777,7 +783,15 @@
         <v>2023</v>
       </c>
       <c r="B13" s="1">
-        <v>5.410905801783176</v>
+        <v>5.375371495025197</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B14" s="1">
+        <v>5.42670428512865</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/charts/0500000US39159.xlsx
+++ b/output_data/charts/0500000US39159.xlsx
@@ -161,47 +161,32 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$14</c:f>
+              <c:f>Sheet1!$A$2:$A$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>2012</c:v>
+                  <c:v>2017</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2013</c:v>
+                  <c:v>2018</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2014</c:v>
+                  <c:v>2019</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2015</c:v>
+                  <c:v>2020</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2016</c:v>
+                  <c:v>2021</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2017</c:v>
+                  <c:v>2022</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2018</c:v>
+                  <c:v>2023</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2019</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>2020</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>2021</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>2022</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>2023</c:v>
-                </c:pt>
-                <c:pt idx="12">
                   <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
@@ -209,48 +194,33 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$14</c:f>
+              <c:f>Sheet1!$B$2:$B$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>2.92184211996499</c:v>
+                  <c:v>3.60626685904272</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.143549252020193</c:v>
+                  <c:v>3.82423655779679</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.05919710489436</c:v>
+                  <c:v>4.016694689541268</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.299422601044817</c:v>
+                  <c:v>4.226935471782958</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.466348227020931</c:v>
+                  <c:v>4.798507774328708</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.607051000564582</c:v>
+                  <c:v>5.206065164891721</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.825017173546494</c:v>
+                  <c:v>5.375371495025197</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.017438659663428</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>4.226935471782958</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>4.800456576511365</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>5.206065164891721</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>5.375371495025197</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>5.42670428512865</c:v>
+                  <c:v>5.431768308857219</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -676,7 +646,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.7109375" style="1" customWidth="1"/>
@@ -692,106 +662,66 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>2012</v>
+        <v>2017</v>
       </c>
       <c r="B2" s="1">
-        <v>2.92184211996499</v>
+        <v>3.60626685904272</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>2013</v>
+        <v>2018</v>
       </c>
       <c r="B3" s="1">
-        <v>3.143549252020193</v>
+        <v>3.82423655779679</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="B4" s="1">
-        <v>3.05919710489436</v>
+        <v>4.016694689541268</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="B5" s="1">
-        <v>3.299422601044817</v>
+        <v>4.226935471782958</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="B6" s="1">
-        <v>3.466348227020931</v>
+        <v>4.798507774328708</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="B7" s="1">
-        <v>3.607051000564582</v>
+        <v>5.206065164891721</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>2018</v>
+        <v>2023</v>
       </c>
       <c r="B8" s="1">
-        <v>3.825017173546494</v>
+        <v>5.375371495025197</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>2019</v>
+        <v>2024</v>
       </c>
       <c r="B9" s="1">
-        <v>4.017438659663428</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="2">
-        <v>2020</v>
-      </c>
-      <c r="B10" s="1">
-        <v>4.226935471782958</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B11" s="1">
-        <v>4.800456576511365</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="2">
-        <v>2022</v>
-      </c>
-      <c r="B12" s="1">
-        <v>5.206065164891721</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="2">
-        <v>2023</v>
-      </c>
-      <c r="B13" s="1">
-        <v>5.375371495025197</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="2">
-        <v>2024</v>
-      </c>
-      <c r="B14" s="1">
-        <v>5.42670428512865</v>
+        <v>5.431768308857219</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/charts/0500000US39159.xlsx
+++ b/output_data/charts/0500000US39159.xlsx
@@ -161,32 +161,47 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$9</c:f>
+              <c:f>Sheet1!$A$2:$A$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>2017</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="6">
                   <c:v>2018</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="7">
                   <c:v>2019</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="8">
                   <c:v>2020</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="9">
                   <c:v>2021</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="10">
                   <c:v>2022</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="11">
                   <c:v>2023</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="12">
                   <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
@@ -194,32 +209,47 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$9</c:f>
+              <c:f>Sheet1!$B$2:$B$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
+                  <c:v>2.830592748468314</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.141700105401357</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.033474658955846</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.265053615617267</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.44976282880552</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>3.60626685904272</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="6">
                   <c:v>3.82423655779679</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="7">
                   <c:v>4.016694689541268</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="8">
                   <c:v>4.226935471782958</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="9">
                   <c:v>4.798507774328708</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="10">
                   <c:v>5.206065164891721</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="11">
                   <c:v>5.375371495025197</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="12">
                   <c:v>5.431768308857219</c:v>
                 </c:pt>
               </c:numCache>
@@ -646,7 +676,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.7109375" style="1" customWidth="1"/>
@@ -662,65 +692,105 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="B2" s="1">
-        <v>3.60626685904272</v>
+        <v>2.830592748468314</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>2018</v>
+        <v>2013</v>
       </c>
       <c r="B3" s="1">
-        <v>3.82423655779679</v>
+        <v>3.141700105401357</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="B4" s="1">
-        <v>4.016694689541268</v>
+        <v>3.033474658955846</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="B5" s="1">
-        <v>4.226935471782958</v>
+        <v>3.265053615617267</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="B6" s="1">
-        <v>4.798507774328708</v>
+        <v>3.44976282880552</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="B7" s="1">
-        <v>5.206065164891721</v>
+        <v>3.60626685904272</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="B8" s="1">
-        <v>5.375371495025197</v>
+        <v>3.82423655779679</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
+        <v>2019</v>
+      </c>
+      <c r="B9" s="1">
+        <v>4.016694689541268</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="2">
+        <v>2020</v>
+      </c>
+      <c r="B10" s="1">
+        <v>4.226935471782958</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="2">
+        <v>2021</v>
+      </c>
+      <c r="B11" s="1">
+        <v>4.798507774328708</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="2">
+        <v>2022</v>
+      </c>
+      <c r="B12" s="1">
+        <v>5.206065164891721</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="2">
+        <v>2023</v>
+      </c>
+      <c r="B13" s="1">
+        <v>5.375371495025197</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="2">
         <v>2024</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B14" s="1">
         <v>5.431768308857219</v>
       </c>
     </row>
